--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136102493</v>
       </c>
       <c r="B4" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136101992</v>
       </c>
       <c r="B5" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80539</v>
+        <v>80541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
